--- a/results/by_outcome/full_results_education_PGI_daughters.xlsx
+++ b/results/by_outcome/full_results_education_PGI_daughters.xlsx
@@ -468,32 +468,32 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>0.610287637661887</v>
+        <v>0.609367268934911</v>
       </c>
       <c r="D2" t="n">
-        <v>0.390476505025163</v>
+        <v>0.390952398601252</v>
       </c>
       <c r="E2" t="n">
-        <v>1.00076414268705</v>
+        <v>1.00031966753616</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="n">
-        <v>0.390178353090004</v>
+        <v>0.390827463748851</v>
       </c>
       <c r="K2" t="n">
-        <v>0.372159945838566</v>
+        <v>0.354105183303147</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0268980770217832</v>
+        <v>0.0282039735379271</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0150658432806</v>
+        <v>0.0555930559456372</v>
       </c>
       <c r="N2" t="n">
-        <v>0.345261868816782</v>
+        <v>0.382309156841074</v>
       </c>
       <c r="O2"/>
     </row>
@@ -508,10 +508,10 @@
       <c r="D3"/>
       <c r="E3"/>
       <c r="F3" t="n">
-        <v>0.568291650936685</v>
+        <v>0.58196943112671</v>
       </c>
       <c r="G3" t="n">
-        <v>0.372444329139591</v>
+        <v>0.354218379234636</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -535,10 +535,10 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>0.59521028192732</v>
+        <v>0.553756441694052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.339991594503761</v>
+        <v>0.35069132639285</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -546,7 +546,7 @@
       <c r="M4"/>
       <c r="N4"/>
       <c r="O4" t="n">
-        <v>0.405244196370604</v>
+        <v>0.446420519694488</v>
       </c>
     </row>
   </sheetData>
@@ -588,16 +588,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.390178353090004</v>
+        <v>0.390827463748851</v>
       </c>
       <c r="D2" t="n">
-        <v>0.305939796124875</v>
+        <v>0.338412831694781</v>
       </c>
       <c r="E2" t="n">
-        <v>0.474416910055133</v>
+        <v>0.443242095802921</v>
       </c>
       <c r="F2" t="n">
-        <v>512</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="3">
@@ -608,16 +608,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.345261868816782</v>
+        <v>0.382309156841074</v>
       </c>
       <c r="D3" t="n">
-        <v>0.254942245626838</v>
+        <v>0.297514724553239</v>
       </c>
       <c r="E3" t="n">
-        <v>0.435581492006727</v>
+        <v>0.467103589128909</v>
       </c>
       <c r="F3" t="n">
-        <v>512</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="4">
@@ -628,16 +628,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.405244196370604</v>
+        <v>0.446420519694488</v>
       </c>
       <c r="D4" t="n">
-        <v>0.302802419248648</v>
+        <v>0.361556340919757</v>
       </c>
       <c r="E4" t="n">
-        <v>0.50768597349256</v>
+        <v>0.531284698469218</v>
       </c>
       <c r="F4" t="n">
-        <v>512</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
